--- a/hotel_management_data.xlsx
+++ b/hotel_management_data.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1916,6 +1916,68 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Oddie</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>the Dog</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>France 23, Paris</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Passport</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2353647</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
